--- a/SGC-CKN/Excel/a1c4e385-d4b3-4cc5-b6f7-483e68438a75_Thi_công_cọc_khoan_nhồi_P11-71_D800_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/a1c4e385-d4b3-4cc5-b6f7-483e68438a75_Thi_công_cọc_khoan_nhồi_P11-71_D800_05-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P11-71</t>
+    <t>P1-71</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
